--- a/Luban/Config/Datas/#SceneConfig.xlsx
+++ b/Luban/Config/Datas/#SceneConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235133F2-0A2E-491A-B7C4-DB85CE76DA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAAD2E3-0C35-4455-BCDD-D5396D3F8A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -197,6 +197,28 @@
   <si>
     <t>1.0,2.0,3.0,4.0|5.0,6.0,7.0,8.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneResource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景资源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scene1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scene2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scene3</t>
+  </si>
+  <si>
+    <t>Scene4</t>
   </si>
 </sst>
 </file>
@@ -594,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -622,7 +644,7 @@
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,8 +693,11 @@
       <c r="P1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -721,8 +746,11 @@
       <c r="P2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -771,8 +799,11 @@
       <c r="P3" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B4" s="3">
         <v>1</v>
       </c>
@@ -795,46 +826,118 @@
       <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B5" s="3"/>
+      <c r="Q4" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
       <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
+      <c r="F5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B6" s="3">
+        <v>3</v>
+      </c>
       <c r="C6" s="3"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
+      <c r="F6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B7" s="3">
+        <v>4</v>
+      </c>
       <c r="C7" s="3"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="2"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
